--- a/data/Terre di Pedemonte/investment_decision/Tegna_MFH_from_2015_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Tegna_MFH_from_2015_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>64.4977794983415</v>
+        <v>20.02402833980714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>8233.601187698785</v>
       </c>
       <c r="F4" t="n">
-        <v>77.77513965661768</v>
+        <v>19.67635294741214</v>
       </c>
       <c r="G4" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="H4" t="n">
-        <v>63.61768076596955</v>
+        <v>20.42185752319337</v>
       </c>
       <c r="I4" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="J4" t="n">
-        <v>77.77513965661768</v>
+        <v>19.1547149094981</v>
       </c>
       <c r="K4" t="n">
         <v>8233.601187698785</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>64.4977794983415</v>
+        <v>20.39407047628902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>8233.601187698785</v>
       </c>
       <c r="F5" t="n">
-        <v>77.77513965661768</v>
+        <v>19.67635294741214</v>
       </c>
       <c r="G5" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="H5" t="n">
-        <v>63.61768076596955</v>
+        <v>21.53287855184001</v>
       </c>
       <c r="I5" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="J5" t="n">
-        <v>77.77513965661768</v>
+        <v>19.57509925108935</v>
       </c>
       <c r="K5" t="n">
         <v>8233.601187698785</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>64.4977794983415</v>
+        <v>25.57922233304343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>8233.601187698785</v>
       </c>
       <c r="F6" t="n">
-        <v>77.77513965661768</v>
+        <v>25.34985543221843</v>
       </c>
       <c r="G6" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="H6" t="n">
-        <v>63.61768076596955</v>
+        <v>26.27592254912524</v>
       </c>
       <c r="I6" t="n">
         <v>8233.601187698785</v>
       </c>
       <c r="J6" t="n">
-        <v>77.77513965661768</v>
+        <v>25.00572264995682</v>
       </c>
       <c r="K6" t="n">
         <v>8233.601187698785</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12.35040178154818</v>
+        <v>32.0262502247191</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.002201578387011138</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.002201578387011138</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004851218355901666</v>
+        <v>0.002201578387011138</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.002201578387011138</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.002928754094117647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.002928754094117647</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004851218355901665</v>
+        <v>0.002928754094117647</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004978881960000001</v>
+        <v>0.003181261857793027</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.006736134416470562</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006736134416470589</v>
+        <v>0.004686006550588235</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7882858000528606</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7672319706315461</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7831238306809645</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I19" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7672821671745237</v>
+        <v>0.4023359985719118</v>
       </c>
       <c r="K19" t="n">
         <v>1.0455652116</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7882858000528606</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7672319706315461</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7831238306809645</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I20" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7672821671745237</v>
+        <v>0.4023359985719118</v>
       </c>
       <c r="K20" t="n">
         <v>1.0455652116</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7882858000528606</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7672319706315461</v>
+        <v>0.4356521714999999</v>
       </c>
       <c r="G21" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7831238306809645</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I21" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7672821671745237</v>
+        <v>0.4023359985719118</v>
       </c>
       <c r="K21" t="n">
         <v>1.0455652116</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0207825184471393</v>
+        <v>0.373416147</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04183634786845376</v>
+        <v>0.373416147</v>
       </c>
       <c r="G29" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H29" t="n">
-        <v>0.02594448781903553</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I29" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04178615132547607</v>
+        <v>0.4067323199280881</v>
       </c>
       <c r="K29" t="n">
         <v>1.0455652116</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0207825184471393</v>
+        <v>0.373416147</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04183634786845375</v>
+        <v>0.373416147</v>
       </c>
       <c r="G30" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H30" t="n">
-        <v>0.02594448781903553</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I30" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J30" t="n">
-        <v>0.04178615132547607</v>
+        <v>0.4067323199280881</v>
       </c>
       <c r="K30" t="n">
         <v>1.0455652116</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0207825184471393</v>
+        <v>0.373416147</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>1.0455652116</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04183634786845376</v>
+        <v>0.373416147</v>
       </c>
       <c r="G31" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02594448781903553</v>
+        <v>0.40453415925</v>
       </c>
       <c r="I31" t="n">
         <v>1.0455652116</v>
       </c>
       <c r="J31" t="n">
-        <v>0.04178615132547607</v>
+        <v>0.4067323199280881</v>
       </c>
       <c r="K31" t="n">
         <v>1.0455652116</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5478257719656568</v>
+        <v>0.5890565873220175</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5500203266117597</v>
+        <v>0.534697468217487</v>
       </c>
       <c r="G54" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5144576194043537</v>
+        <v>0.5922308843879317</v>
       </c>
       <c r="I54" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5183642196627649</v>
+        <v>0.5275128585097575</v>
       </c>
       <c r="K54" t="n">
         <v>2.654526044119942</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.5478257719656568</v>
+        <v>0.5890565873220175</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5500203266117597</v>
+        <v>0.534697468217487</v>
       </c>
       <c r="G55" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5144576194043537</v>
+        <v>0.5922308843879317</v>
       </c>
       <c r="I55" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5183642196627649</v>
+        <v>0.5275128585097575</v>
       </c>
       <c r="K55" t="n">
         <v>2.654526044119942</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5478257719656568</v>
+        <v>0.5890565873220175</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5500203266117597</v>
+        <v>0.534697468217487</v>
       </c>
       <c r="G56" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5144576194043537</v>
+        <v>0.5922308843879317</v>
       </c>
       <c r="I56" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5183642196627649</v>
+        <v>0.5275128585097575</v>
       </c>
       <c r="K56" t="n">
         <v>2.654526044119942</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5361882377508861</v>
+        <v>0.3729624462404147</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4717560573628637</v>
+        <v>0.4315775073444196</v>
       </c>
       <c r="G64" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5736818531201827</v>
+        <v>0.3649182677643529</v>
       </c>
       <c r="I64" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5034121643118585</v>
+        <v>0.4451475595730844</v>
       </c>
       <c r="K64" t="n">
         <v>2.654526044119942</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.5361882377508861</v>
+        <v>0.3729624462404147</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4717560573628637</v>
+        <v>0.4315775073444196</v>
       </c>
       <c r="G65" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5736818531201827</v>
+        <v>0.3649182677643529</v>
       </c>
       <c r="I65" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5034121643118585</v>
+        <v>0.4451475595730844</v>
       </c>
       <c r="K65" t="n">
         <v>2.654526044119942</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.5361882377508861</v>
+        <v>0.3729624462404147</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>2.654526044119942</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4717560573628637</v>
+        <v>0.4315775073444196</v>
       </c>
       <c r="G66" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5736818531201827</v>
+        <v>0.3649182677643529</v>
       </c>
       <c r="I66" t="n">
         <v>2.654526044119942</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5034121643118585</v>
+        <v>0.4451475595730844</v>
       </c>
       <c r="K66" t="n">
         <v>2.654526044119942</v>
